--- a/dashboard_rafa/task rafael.xlsx
+++ b/dashboard_rafa/task rafael.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enforcegestaoativos-my.sharepoint.com/personal/vinicius_ibiapina_enforcegroup_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A63E0F4E-1C49-4776-A6F6-E14F40F9B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{A63E0F4E-1C49-4776-A6F6-E14F40F9B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35D3C5FB-4840-4A32-8767-5A925BEDFDC0}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{A4455C31-2650-4192-9032-D54DD4200697}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4455C31-2650-4192-9032-D54DD4200697}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$B$1:$B$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$AE$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -71,6 +72,24 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={385B178E-9D7D-456E-A71A-D11424470549}</author>
+  </authors>
+  <commentList>
+    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{385B178E-9D7D-456E-A71A-D11424470549}">
+      <text>
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
+    30% na assinatura e o restante será pago na escritura, correção por CDI</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -94,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="149">
   <si>
     <t>Destinação</t>
   </si>
@@ -478,6 +497,69 @@
   </si>
   <si>
     <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Tabela GI</t>
+  </si>
+  <si>
+    <t>Equip.</t>
+  </si>
+  <si>
+    <t>Vendido</t>
+  </si>
+  <si>
+    <t>Não Vendido</t>
+  </si>
+  <si>
+    <t>Proposta em Negociação</t>
+  </si>
+  <si>
+    <t>Proposta em Fase de Minuta</t>
+  </si>
+  <si>
+    <t>Proposta distante</t>
+  </si>
+  <si>
+    <t>Proposta em negociação - tabela de GI</t>
+  </si>
+  <si>
+    <t>Vendido (Integrada)</t>
+  </si>
+  <si>
+    <t>Em minuta</t>
+  </si>
+  <si>
+    <t>Em aprovação (comitê)</t>
+  </si>
+  <si>
+    <t>Aguardando formalização</t>
+  </si>
+  <si>
+    <t>Negociação em andamento</t>
+  </si>
+  <si>
+    <t>Arrendatário plantou eucalipto</t>
+  </si>
+  <si>
+    <t>Sem proposta</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>NÃO LIBERADO</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Obs</t>
+  </si>
+  <si>
+    <t>Proposta</t>
+  </si>
+  <si>
+    <t>Não tem</t>
   </si>
 </sst>
 </file>
@@ -541,12 +623,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Aptos Narrow"/>
@@ -560,8 +636,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -598,8 +678,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -644,12 +766,75 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -694,16 +879,16 @@
     <xf numFmtId="4" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -724,17 +909,86 @@
     <xf numFmtId="4" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="8" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3774,7 +4028,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Renan Solimeo" id="{88F232AA-9CB9-42D7-B0C6-18069277159E}" userId="S::renan.solimeo@enforcegroup.com.br::4314c441-2dc5-472d-860b-5722a7b33b27" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4105,45 +4361,58 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="B33" dT="2026-02-09T14:13:44.92" personId="{88F232AA-9CB9-42D7-B0C6-18069277159E}" id="{385B178E-9D7D-456E-A71A-D11424470549}">
+    <text>30% na assinatura e o restante será pago na escritura, correção por CDI</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82245A8F-1FD0-452B-9FFD-060B40FA72CD}">
-  <dimension ref="A1:AE39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AI39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.90625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="33.90625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="23" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="37.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4237,8 +4506,20 @@
       <c r="AE1" s="8" t="s">
         <v>28</v>
       </c>
+      <c r="AF1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
@@ -4335,8 +4616,20 @@
         <f t="array" aca="1" ref="AE2" ca="1">IFERROR([2]!CalculateINPC(AD2,[1]DT_BASE!$C$3,-1)*AC2,0)</f>
         <v>0</v>
       </c>
+      <c r="AF2" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH2" s="47">
+        <v>25000000</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>30</v>
       </c>
@@ -4432,8 +4725,15 @@
       <c r="AE3" s="29">
         <v>0</v>
       </c>
+      <c r="AF3" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG3" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH3" s="48"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
@@ -4530,8 +4830,15 @@
         <f t="array" aca="1" ref="AE4" ca="1">IFERROR([2]!CalculateINPC(AD4,[1]DT_BASE!$C$3,-1)*AC4,0)</f>
         <v>0</v>
       </c>
+      <c r="AF4" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG4" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH4" s="46"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>30</v>
       </c>
@@ -4628,8 +4935,20 @@
         <f t="array" aca="1" ref="AE5" ca="1">IFERROR([2]!CalculateINPC(AD5,[1]DT_BASE!$C$3,-1)*AC5,0)</f>
         <v>0</v>
       </c>
+      <c r="AF5" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG5" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="49">
+        <v>45000000</v>
+      </c>
+      <c r="AI5">
+        <v>6000000</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
@@ -4726,8 +5045,20 @@
         <f t="array" aca="1" ref="AE6" ca="1">IFERROR([2]!CalculateINPC(AD6,[1]DT_BASE!$C$3,-1)*AC6,0)</f>
         <v>0</v>
       </c>
+      <c r="AF6" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG6" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH6" s="50" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI6">
+        <v>26000000</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>30</v>
       </c>
@@ -4824,8 +5155,20 @@
         <f t="array" aca="1" ref="AE7" ca="1">IFERROR([2]!CalculateINPC(AD7,[1]DT_BASE!$C$3,-1)*AC7,0)</f>
         <v>0</v>
       </c>
+      <c r="AF7" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG7" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH7" s="49">
+        <v>22500000</v>
+      </c>
+      <c r="AI7">
+        <v>13000000</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
@@ -4922,8 +5265,15 @@
         <f t="array" aca="1" ref="AE8" ca="1">IFERROR([2]!CalculateINPC(AD8,[1]DT_BASE!$C$3,-1)*AC8,0)</f>
         <v>0</v>
       </c>
+      <c r="AF8" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG8" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH8" s="46"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>30</v>
       </c>
@@ -5020,8 +5370,20 @@
         <f t="array" aca="1" ref="AE9" ca="1">IFERROR([2]!CalculateINPC(AD9,[1]DT_BASE!$C$3,-1)*AC9,0)</f>
         <v>0</v>
       </c>
+      <c r="AF9" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG9" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH9" s="49">
+        <v>13000000</v>
+      </c>
+      <c r="AI9">
+        <v>10000000</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>30</v>
       </c>
@@ -5118,8 +5480,15 @@
         <f t="array" aca="1" ref="AE10" ca="1">IFERROR([2]!CalculateINPC(AD10,[1]DT_BASE!$C$3,-1)*AC10,0)</f>
         <v>0</v>
       </c>
+      <c r="AF10" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG10" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH10" s="46"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
@@ -5216,8 +5585,15 @@
         <f t="array" aca="1" ref="AE11" ca="1">IFERROR([2]!CalculateINPC(AD11,[1]DT_BASE!$C$3,-1)*AC11,0)</f>
         <v>0</v>
       </c>
+      <c r="AF11" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG11" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH11" s="46"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
@@ -5312,8 +5688,20 @@
         <f t="array" aca="1" ref="AE12" ca="1">IFERROR([2]!CalculateINPC(AD12,[1]DT_BASE!$C$3,-1)*AC12,0)</f>
         <v>0</v>
       </c>
+      <c r="AF12" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG12" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH12" s="51">
+        <v>18000000</v>
+      </c>
+      <c r="AI12" s="51">
+        <v>18000000</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>30</v>
       </c>
@@ -5410,8 +5798,18 @@
         <f t="array" aca="1" ref="AE13" ca="1">IFERROR([2]!CalculateINPC(AD13,[1]DT_BASE!$C$3,-1)*AC13,0)</f>
         <v>0</v>
       </c>
+      <c r="AF13" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG13" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH13" s="52"/>
+      <c r="AI13">
+        <v>7000000</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
@@ -5508,8 +5906,15 @@
         <f t="array" aca="1" ref="AE14" ca="1">IFERROR([2]!CalculateINPC(AD14,[1]DT_BASE!$C$3,-1)*AC14,0)</f>
         <v>0</v>
       </c>
+      <c r="AF14" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG14" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH14" s="46"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>30</v>
       </c>
@@ -5606,8 +6011,15 @@
         <f t="array" aca="1" ref="AE15" ca="1">IFERROR([2]!CalculateINPC(AD15,[1]DT_BASE!$C$3,-1)*AC15,0)</f>
         <v>0</v>
       </c>
+      <c r="AF15" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG15" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH15" s="50"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -5704,8 +6116,17 @@
         <f t="array" aca="1" ref="AE16" ca="1">IFERROR([2]!CalculateINPC(AD16,[1]DT_BASE!$C$3,-1)*AC16,0)</f>
         <v>0</v>
       </c>
+      <c r="AF16" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG16" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH16" s="50" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>30</v>
       </c>
@@ -5802,8 +6223,15 @@
         <f t="array" aca="1" ref="AE17" ca="1">IFERROR([2]!CalculateINPC(AD17,[1]DT_BASE!$C$3,-1)*AC17,0)</f>
         <v>0</v>
       </c>
+      <c r="AF17" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG17" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH17" s="50"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>30</v>
       </c>
@@ -5900,8 +6328,20 @@
         <f t="array" aca="1" ref="AE18" ca="1">IFERROR([2]!CalculateINPC(AD18,[1]DT_BASE!$C$3,-1)*AC18,0)</f>
         <v>0</v>
       </c>
+      <c r="AF18" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG18" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH18" s="49">
+        <v>5200000</v>
+      </c>
+      <c r="AI18">
+        <v>3500000</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
@@ -5998,8 +6438,17 @@
         <f t="array" aca="1" ref="AE19" ca="1">IFERROR([2]!CalculateINPC(AD19,[1]DT_BASE!$C$3,-1)*AC19,0)</f>
         <v>0</v>
       </c>
+      <c r="AF19" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG19" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH19" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>30</v>
       </c>
@@ -6096,8 +6545,15 @@
         <f t="array" aca="1" ref="AE20" ca="1">IFERROR([2]!CalculateINPC(AD20,[1]DT_BASE!$C$3,-1)*AC20,0)</f>
         <v>0</v>
       </c>
+      <c r="AF20" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG20" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH20" s="46"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>30</v>
       </c>
@@ -6194,8 +6650,15 @@
         <f t="array" aca="1" ref="AE21" ca="1">IFERROR([2]!CalculateINPC(AD21,[1]DT_BASE!$C$3,-1)*AC21,0)</f>
         <v>0</v>
       </c>
+      <c r="AF21" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG21" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH21" s="50"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
@@ -6290,8 +6753,20 @@
         <f t="array" aca="1" ref="AE22" ca="1">IFERROR([2]!CalculateINPC(AD22,[1]DT_BASE!$C$3,-1)*AC22,0)</f>
         <v>0</v>
       </c>
+      <c r="AF22" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG22" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH22" s="49">
+        <v>2500000</v>
+      </c>
+      <c r="AI22">
+        <v>2200000</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>30</v>
       </c>
@@ -6386,8 +6861,20 @@
         <f t="array" aca="1" ref="AE23" ca="1">IFERROR([2]!CalculateINPC(AD23,[1]DT_BASE!$C$3,-1)*AC23,0)</f>
         <v>0</v>
       </c>
+      <c r="AF23" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG23" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH23" s="47">
+        <v>10500000</v>
+      </c>
+      <c r="AI23">
+        <v>4000000</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>30</v>
       </c>
@@ -6484,8 +6971,17 @@
         <f t="array" aca="1" ref="AE24" ca="1">IFERROR([2]!CalculateINPC(AD24,[1]DT_BASE!$C$3,-1)*AC24,0)</f>
         <v>0</v>
       </c>
+      <c r="AF24" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG24" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH24" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>30</v>
       </c>
@@ -6582,8 +7078,17 @@
         <f t="array" aca="1" ref="AE25" ca="1">IFERROR([2]!CalculateINPC(AD25,[1]DT_BASE!$C$3,-1)*AC25,0)</f>
         <v>0</v>
       </c>
+      <c r="AF25" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG25" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH25" s="47">
+        <v>1600000</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
@@ -6680,8 +7185,18 @@
         <f t="array" aca="1" ref="AE26" ca="1">IFERROR([2]!CalculateINPC(AD26,[1]DT_BASE!$C$3,-1)*AC26,0)</f>
         <v>0</v>
       </c>
+      <c r="AF26" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG26" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="AH26" s="50"/>
+      <c r="AI26">
+        <v>900000</v>
+      </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6778,8 +7293,20 @@
         <f t="array" aca="1" ref="AE27" ca="1">IFERROR([2]!CalculateINPC(AD27,[1]DT_BASE!$C$3,-1)*AC27,0)</f>
         <v>0</v>
       </c>
+      <c r="AF27" s="48" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG27" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH27" s="49">
+        <v>12000000</v>
+      </c>
+      <c r="AI27">
+        <v>8000000</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>30</v>
       </c>
@@ -6876,8 +7403,17 @@
         <f t="array" aca="1" ref="AE28" ca="1">IFERROR([2]!CalculateINPC(AD28,[1]DT_BASE!$C$3,-1)*AC28,0)</f>
         <v>0</v>
       </c>
+      <c r="AF28" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG28" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH28" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>30</v>
       </c>
@@ -6972,8 +7508,15 @@
         <f t="array" aca="1" ref="AE29" ca="1">IFERROR([2]!CalculateINPC(AD29,[1]DT_BASE!$C$3,-1)*AC29,0)</f>
         <v>0</v>
       </c>
+      <c r="AF29" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG29" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH29" s="46"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>30</v>
       </c>
@@ -7068,8 +7611,17 @@
         <f t="array" aca="1" ref="AE30" ca="1">IFERROR([2]!CalculateINPC(AD30,[1]DT_BASE!$C$3,-1)*AC30,0)</f>
         <v>0</v>
       </c>
+      <c r="AF30" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG30" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH30" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>30</v>
       </c>
@@ -7164,8 +7716,15 @@
         <f t="array" aca="1" ref="AE31" ca="1">IFERROR([2]!CalculateINPC(AD31,[1]DT_BASE!$C$3,-1)*AC31,0)/2750000</f>
         <v>0</v>
       </c>
+      <c r="AF31" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG31" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH31" s="46"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>30</v>
       </c>
@@ -7262,8 +7821,20 @@
         <f t="array" aca="1" ref="AE32" ca="1">IFERROR([2]!CalculateINPC(AD32,[1]DT_BASE!$C$3,-1)*AC32,0)</f>
         <v>0</v>
       </c>
+      <c r="AF32" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG32" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH32" s="47">
+        <v>1980000</v>
+      </c>
+      <c r="AI32">
+        <v>1500000</v>
+      </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>30</v>
       </c>
@@ -7360,8 +7931,17 @@
         <f t="array" aca="1" ref="AE33" ca="1">IFERROR([2]!CalculateINPC(AD33,[1]DT_BASE!$C$3,-1)*AC33,0)</f>
         <v>0</v>
       </c>
+      <c r="AF33" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG33" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH33" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>30</v>
       </c>
@@ -7460,8 +8040,17 @@
         <f t="array" aca="1" ref="AE34" ca="1">IFERROR([2]!CalculateINPC(AD34,[1]DT_BASE!$C$3,-1)*AC34,0)</f>
         <v>0</v>
       </c>
+      <c r="AF34" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG34" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH34" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>30</v>
       </c>
@@ -7556,8 +8145,17 @@
         <f t="array" aca="1" ref="AE35" ca="1">IFERROR([2]!CalculateINPC(AD35,[1]DT_BASE!$C$3,-1)*AC35,0)</f>
         <v>0</v>
       </c>
+      <c r="AF35" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG35" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH35" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>30</v>
       </c>
@@ -7652,8 +8250,17 @@
         <f t="array" aca="1" ref="AE36" ca="1">IFERROR([2]!CalculateINPC(AD36,[1]DT_BASE!$C$3,-1)*AC36,0)</f>
         <v>0</v>
       </c>
+      <c r="AF36" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG36" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH36" s="46" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>30</v>
       </c>
@@ -7752,8 +8359,17 @@
         <f t="array" aca="1" ref="AE37" ca="1">IFERROR([2]!CalculateINPC(AD37,[1]DT_BASE!$C$3,-1)*AC37,0)</f>
         <v>0</v>
       </c>
+      <c r="AF37" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG37" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH37" s="46" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>30</v>
       </c>
@@ -7847,8 +8463,17 @@
       <c r="AE38" s="27" t="s">
         <v>37</v>
       </c>
+      <c r="AF38" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG38" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH38" s="46" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>30</v>
       </c>
@@ -7942,6 +8567,638 @@
       <c r="AE39" s="15" cm="1">
         <f t="array" aca="1" ref="AE39" ca="1">IFERROR([2]!CalculateINPC(AD39,[1]DT_BASE!$C$3,-1)*AC39,0)</f>
         <v>0</v>
+      </c>
+      <c r="AF39" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG39" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH39" s="46"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AE39" xr:uid="{82245A8F-1FD0-452B-9FFD-060B40FA72CD}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="25510"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A826AB59-3EB8-4F7C-AA66-A343392DE3EB}">
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="30">
+        <v>6896</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="41">
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="31">
+        <v>8112</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="42">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="43">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="44">
+        <v>22500000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="31">
+        <v>26999</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="44">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="31">
+        <v>35948</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="44">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="31">
+        <v>20496</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="44">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="44">
+        <v>10500000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="31">
+        <v>11142</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="31">
+        <v>4379</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="42">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="31">
+        <v>1453</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="44">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="31">
+        <v>2629</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="31">
+        <v>7632</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="31">
+        <v>3222</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="44">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="31">
+        <v>7047</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="31">
+        <v>51</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="31">
+        <v>147628</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="31">
+        <v>11444</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="31">
+        <v>15927</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="33">
+        <v>23697</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="33">
+        <v>9846</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="33">
+        <v>5377</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="33">
+        <v>4479</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="33">
+        <v>6193</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="33">
+        <v>579</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="34">
+        <v>1615</v>
+      </c>
+      <c r="B33" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="34">
+        <v>25510</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="34">
+        <v>8701</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="31">
+        <v>145993</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="31">
+        <v>146005</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="31">
+        <v>2164</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="31">
+        <v>10565</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="32">
+        <v>3495</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="31" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" s="31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" s="31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="31" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard_rafa/task rafael.xlsx
+++ b/dashboard_rafa/task rafael.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enforcegestaoativos-my.sharepoint.com/personal/vinicius_ibiapina_enforcegroup_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{A63E0F4E-1C49-4776-A6F6-E14F40F9B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35D3C5FB-4840-4A32-8767-5A925BEDFDC0}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{A63E0F4E-1C49-4776-A6F6-E14F40F9B856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3414D0C-3FAA-4C38-BCD4-31A1102E8D9C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4455C31-2650-4192-9032-D54DD4200697}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4455C31-2650-4192-9032-D54DD4200697}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
-    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
+    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$AE$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$AJ$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,24 +71,6 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={385B178E-9D7D-456E-A71A-D11424470549}</author>
-  </authors>
-  <commentList>
-    <comment ref="B33" authorId="0" shapeId="0" xr:uid="{385B178E-9D7D-456E-A71A-D11424470549}">
-      <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
-    30% na assinatura e o restante será pago na escritura, correção por CDI</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -113,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="165">
   <si>
     <t>Destinação</t>
   </si>
@@ -502,9 +483,6 @@
     <t>Tabela GI</t>
   </si>
   <si>
-    <t>Equip.</t>
-  </si>
-  <si>
     <t>Vendido</t>
   </si>
   <si>
@@ -544,9 +522,6 @@
     <t>Sem proposta</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>NÃO LIBERADO</t>
   </si>
   <si>
@@ -559,14 +534,72 @@
     <t>Proposta</t>
   </si>
   <si>
-    <t>Não tem</t>
+    <t>Natureza</t>
+  </si>
+  <si>
+    <t>Valor da Garantia</t>
+  </si>
+  <si>
+    <t>EXPROPRIAÇÃO</t>
+  </si>
+  <si>
+    <t>Comprador</t>
+  </si>
+  <si>
+    <t>MC Icorporações</t>
+  </si>
+  <si>
+    <t>Empresário da cidade</t>
+  </si>
+  <si>
+    <t>Investidor e Incorporadora</t>
+  </si>
+  <si>
+    <t>Investidor local e comodatário</t>
+  </si>
+  <si>
+    <t>Cooperativa INTEGRADA</t>
+  </si>
+  <si>
+    <t>Eucamed</t>
+  </si>
+  <si>
+    <t>Cooperativa Agricola de Canoinhas</t>
+  </si>
+  <si>
+    <t>Previsão de registro</t>
+  </si>
+  <si>
+    <t>AGUARDANDO DEFINIÇÃO QUANTO AO PAGAMENTO DAS DÍVIDAS DA CAC</t>
+  </si>
+  <si>
+    <t>25/05/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>26/04/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>13/04/2026</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,8 +673,19 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,24 +724,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -720,8 +746,14 @@
         <bgColor rgb="FFBDD7EE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -768,54 +800,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
@@ -829,12 +813,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -921,77 +921,57 @@
     <xf numFmtId="4" fontId="6" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="9" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="8" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="9" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="1" xr:uid="{D4042694-D64D-4030-8C3A-D1D4276D7D50}"/>
   </cellStyles>
@@ -4025,12 +4005,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Renan Solimeo" id="{88F232AA-9CB9-42D7-B0C6-18069277159E}" userId="S::renan.solimeo@enforcegroup.com.br::4314c441-2dc5-472d-860b-5722a7b33b27" providerId="AD"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4361,18 +4335,9 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B33" dT="2026-02-09T14:13:44.92" personId="{88F232AA-9CB9-42D7-B0C6-18069277159E}" id="{385B178E-9D7D-456E-A71A-D11424470549}">
-    <text>30% na assinatura e o restante será pago na escritura, correção por CDI</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82245A8F-1FD0-452B-9FFD-060B40FA72CD}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AN39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -4408,11 +4373,16 @@
     <col min="31" max="31" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.85546875" style="38" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="16.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.28515625" style="38" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4507,19 +4477,31 @@
         <v>28</v>
       </c>
       <c r="AF1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AH1" t="s">
         <v>128</v>
       </c>
       <c r="AI1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK1" s="38" t="s">
         <v>147</v>
       </c>
+      <c r="AL1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>157</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
@@ -4616,20 +4598,23 @@
         <f t="array" aca="1" ref="AE2" ca="1">IFERROR([2]!CalculateINPC(AD2,[1]DT_BASE!$C$3,-1)*AC2,0)</f>
         <v>0</v>
       </c>
-      <c r="AF2" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG2" s="46" t="s">
+      <c r="AF2" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH2" s="47">
+      <c r="AH2" s="35">
         <v>25000000</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" s="38" t="s">
         <v>148</v>
       </c>
+      <c r="AK2" s="38">
+        <v>30350000</v>
+      </c>
     </row>
-    <row r="3" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>30</v>
       </c>
@@ -4725,15 +4710,22 @@
       <c r="AE3" s="29">
         <v>0</v>
       </c>
-      <c r="AF3" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG3" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH3" s="48"/>
+      <c r="AF3" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG3" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH3" s="36"/>
+      <c r="AI3" s="38">
+        <v>11000000</v>
+      </c>
+      <c r="AM3" s="45">
+        <v>46107</v>
+      </c>
+      <c r="AN3" s="45"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>30</v>
       </c>
@@ -4830,15 +4822,22 @@
         <f t="array" aca="1" ref="AE4" ca="1">IFERROR([2]!CalculateINPC(AD4,[1]DT_BASE!$C$3,-1)*AC4,0)</f>
         <v>0</v>
       </c>
-      <c r="AF4" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG4" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="AH4" s="46"/>
+      <c r="AF4" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG4" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH4" s="35"/>
+      <c r="AI4" s="38">
+        <v>13000000</v>
+      </c>
+      <c r="AM4" s="45">
+        <v>46107</v>
+      </c>
+      <c r="AN4" s="45"/>
     </row>
-    <row r="5" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>30</v>
       </c>
@@ -4935,20 +4934,23 @@
         <f t="array" aca="1" ref="AE5" ca="1">IFERROR([2]!CalculateINPC(AD5,[1]DT_BASE!$C$3,-1)*AC5,0)</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG5" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="AH5" s="49">
+      <c r="AF5" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG5" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH5" s="36">
         <v>45000000</v>
       </c>
-      <c r="AI5">
+      <c r="AI5" s="38">
         <v>6000000</v>
       </c>
+      <c r="AM5" s="46">
+        <v>46204</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>30</v>
       </c>
@@ -4997,8 +4999,8 @@
       <c r="P6" s="15" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Q6" s="15" t="e">
-        <v>#N/A</v>
+      <c r="Q6" s="15">
+        <v>0</v>
       </c>
       <c r="R6" s="15" t="e">
         <v>#N/A</v>
@@ -5045,20 +5047,29 @@
         <f t="array" aca="1" ref="AE6" ca="1">IFERROR([2]!CalculateINPC(AD6,[1]DT_BASE!$C$3,-1)*AC6,0)</f>
         <v>0</v>
       </c>
-      <c r="AF6" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG6" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH6" s="50" t="s">
+      <c r="AF6" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG6" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH6" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="AI6">
+      <c r="AI6" s="38">
         <v>26000000</v>
       </c>
+      <c r="AJ6" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK6" s="38">
+        <v>60003000</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>30</v>
       </c>
@@ -5155,20 +5166,29 @@
         <f t="array" aca="1" ref="AE7" ca="1">IFERROR([2]!CalculateINPC(AD7,[1]DT_BASE!$C$3,-1)*AC7,0)</f>
         <v>0</v>
       </c>
-      <c r="AF7" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG7" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH7" s="49">
+      <c r="AF7" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG7" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH7" s="36">
         <v>22500000</v>
       </c>
-      <c r="AI7">
+      <c r="AI7" s="38">
         <v>13000000</v>
       </c>
+      <c r="AJ7" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK7" s="38">
+        <v>11730000</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>151</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
@@ -5265,15 +5285,21 @@
         <f t="array" aca="1" ref="AE8" ca="1">IFERROR([2]!CalculateINPC(AD8,[1]DT_BASE!$C$3,-1)*AC8,0)</f>
         <v>0</v>
       </c>
-      <c r="AF8" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG8" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH8" s="46"/>
+      <c r="AF8" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG8" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH8" s="35"/>
+      <c r="AJ8" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK8" s="38">
+        <v>3420000</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>30</v>
       </c>
@@ -5370,20 +5396,26 @@
         <f t="array" aca="1" ref="AE9" ca="1">IFERROR([2]!CalculateINPC(AD9,[1]DT_BASE!$C$3,-1)*AC9,0)</f>
         <v>0</v>
       </c>
-      <c r="AF9" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG9" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH9" s="49">
+      <c r="AF9" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG9" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH9" s="36">
         <v>13000000</v>
       </c>
-      <c r="AI9">
+      <c r="AI9" s="38">
         <v>10000000</v>
       </c>
+      <c r="AJ9" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK9" s="38">
+        <v>7030000</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>30</v>
       </c>
@@ -5480,15 +5512,21 @@
         <f t="array" aca="1" ref="AE10" ca="1">IFERROR([2]!CalculateINPC(AD10,[1]DT_BASE!$C$3,-1)*AC10,0)</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG10" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="AH10" s="46"/>
+      <c r="AF10" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG10" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH10" s="35"/>
+      <c r="AJ10" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK10" s="38">
+        <v>5407000</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>30</v>
       </c>
@@ -5585,15 +5623,18 @@
         <f t="array" aca="1" ref="AE11" ca="1">IFERROR([2]!CalculateINPC(AD11,[1]DT_BASE!$C$3,-1)*AC11,0)</f>
         <v>0</v>
       </c>
-      <c r="AF11" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG11" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH11" s="46"/>
+      <c r="AF11" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG11" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH11" s="35"/>
+      <c r="AM11" s="45">
+        <v>46167</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
@@ -5688,20 +5729,27 @@
         <f t="array" aca="1" ref="AE12" ca="1">IFERROR([2]!CalculateINPC(AD12,[1]DT_BASE!$C$3,-1)*AC12,0)</f>
         <v>0</v>
       </c>
-      <c r="AF12" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG12" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AH12" s="51">
+      <c r="AF12" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG12" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH12" s="37">
         <v>18000000</v>
       </c>
-      <c r="AI12" s="51">
+      <c r="AI12" s="39">
         <v>18000000</v>
       </c>
+      <c r="AJ12" s="42"/>
+      <c r="AL12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM12" s="46">
+        <v>46204</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>30</v>
       </c>
@@ -5798,18 +5846,24 @@
         <f t="array" aca="1" ref="AE13" ca="1">IFERROR([2]!CalculateINPC(AD13,[1]DT_BASE!$C$3,-1)*AC13,0)</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="52" t="s">
-        <v>133</v>
-      </c>
-      <c r="AG13" s="52" t="s">
-        <v>137</v>
-      </c>
-      <c r="AH13" s="52"/>
-      <c r="AI13">
+      <c r="AF13" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="AG13" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="AH13" s="34"/>
+      <c r="AI13" s="38">
         <v>7000000</v>
       </c>
+      <c r="AL13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM13" s="45">
+        <v>46125</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
@@ -5906,15 +5960,18 @@
         <f t="array" aca="1" ref="AE14" ca="1">IFERROR([2]!CalculateINPC(AD14,[1]DT_BASE!$C$3,-1)*AC14,0)</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG14" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH14" s="46"/>
+      <c r="AF14" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG14" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH14" s="30"/>
+      <c r="AM14" s="45">
+        <v>46167</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>30</v>
       </c>
@@ -6011,15 +6068,24 @@
         <f t="array" aca="1" ref="AE15" ca="1">IFERROR([2]!CalculateINPC(AD15,[1]DT_BASE!$C$3,-1)*AC15,0)</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG15" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH15" s="50"/>
+      <c r="AF15" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG15" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH15" s="33"/>
+      <c r="AJ15" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK15" s="38">
+        <v>1221000</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>30</v>
       </c>
@@ -6116,17 +6182,23 @@
         <f t="array" aca="1" ref="AE16" ca="1">IFERROR([2]!CalculateINPC(AD16,[1]DT_BASE!$C$3,-1)*AC16,0)</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG16" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH16" s="50" t="s">
+      <c r="AF16" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG16" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH16" s="33" t="s">
         <v>37</v>
       </c>
+      <c r="AL16" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM16" s="45">
+        <v>46297</v>
+      </c>
     </row>
-    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>30</v>
       </c>
@@ -6223,15 +6295,21 @@
         <f t="array" aca="1" ref="AE17" ca="1">IFERROR([2]!CalculateINPC(AD17,[1]DT_BASE!$C$3,-1)*AC17,0)</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG17" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH17" s="50"/>
+      <c r="AF17" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG17" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH17" s="33"/>
+      <c r="AL17" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM17" s="45">
+        <v>46297</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>30</v>
       </c>
@@ -6328,20 +6406,26 @@
         <f t="array" aca="1" ref="AE18" ca="1">IFERROR([2]!CalculateINPC(AD18,[1]DT_BASE!$C$3,-1)*AC18,0)</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG18" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH18" s="49">
+      <c r="AF18" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG18" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH18" s="40">
         <v>5200000</v>
       </c>
-      <c r="AI18">
+      <c r="AI18" s="38">
         <v>3500000</v>
       </c>
+      <c r="AL18" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM18" s="45">
+        <v>46107</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>30</v>
       </c>
@@ -6438,17 +6522,20 @@
         <f t="array" aca="1" ref="AE19" ca="1">IFERROR([2]!CalculateINPC(AD19,[1]DT_BASE!$C$3,-1)*AC19,0)</f>
         <v>0</v>
       </c>
-      <c r="AF19" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG19" s="46" t="s">
+      <c r="AF19" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG19" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH19" s="46" t="s">
-        <v>144</v>
+      <c r="AH19" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM19" s="45">
+        <v>46107</v>
       </c>
     </row>
-    <row r="20" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>30</v>
       </c>
@@ -6545,15 +6632,18 @@
         <f t="array" aca="1" ref="AE20" ca="1">IFERROR([2]!CalculateINPC(AD20,[1]DT_BASE!$C$3,-1)*AC20,0)</f>
         <v>0</v>
       </c>
-      <c r="AF20" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG20" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH20" s="46"/>
+      <c r="AF20" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG20" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH20" s="30"/>
+      <c r="AM20" s="45">
+        <v>46138</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>30</v>
       </c>
@@ -6650,15 +6740,24 @@
         <f t="array" aca="1" ref="AE21" ca="1">IFERROR([2]!CalculateINPC(AD21,[1]DT_BASE!$C$3,-1)*AC21,0)</f>
         <v>0</v>
       </c>
-      <c r="AF21" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG21" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH21" s="50"/>
+      <c r="AF21" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG21" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH21" s="33"/>
+      <c r="AJ21" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK21" s="38">
+        <v>1654000</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>30</v>
       </c>
@@ -6753,20 +6852,26 @@
         <f t="array" aca="1" ref="AE22" ca="1">IFERROR([2]!CalculateINPC(AD22,[1]DT_BASE!$C$3,-1)*AC22,0)</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG22" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH22" s="49">
+      <c r="AF22" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG22" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH22" s="40">
         <v>2500000</v>
       </c>
-      <c r="AI22">
+      <c r="AI22" s="38">
         <v>2200000</v>
       </c>
+      <c r="AL22" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM22" s="45">
+        <v>46087</v>
+      </c>
     </row>
-    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>30</v>
       </c>
@@ -6861,20 +6966,23 @@
         <f t="array" aca="1" ref="AE23" ca="1">IFERROR([2]!CalculateINPC(AD23,[1]DT_BASE!$C$3,-1)*AC23,0)</f>
         <v>0</v>
       </c>
-      <c r="AF23" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG23" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH23" s="47">
+      <c r="AF23" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG23" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH23" s="41">
         <v>10500000</v>
       </c>
-      <c r="AI23">
+      <c r="AI23" s="38">
         <v>4000000</v>
       </c>
+      <c r="AM23" t="s">
+        <v>158</v>
+      </c>
     </row>
-    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>30</v>
       </c>
@@ -6971,17 +7079,20 @@
         <f t="array" aca="1" ref="AE24" ca="1">IFERROR([2]!CalculateINPC(AD24,[1]DT_BASE!$C$3,-1)*AC24,0)</f>
         <v>0</v>
       </c>
-      <c r="AF24" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG24" s="46" t="s">
+      <c r="AF24" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG24" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH24" s="46" t="s">
-        <v>144</v>
+      <c r="AH24" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM24" s="45">
+        <v>46192</v>
       </c>
     </row>
-    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>30</v>
       </c>
@@ -7078,17 +7189,23 @@
         <f t="array" aca="1" ref="AE25" ca="1">IFERROR([2]!CalculateINPC(AD25,[1]DT_BASE!$C$3,-1)*AC25,0)</f>
         <v>0</v>
       </c>
-      <c r="AF25" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG25" s="46" t="s">
+      <c r="AF25" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG25" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH25" s="47">
+      <c r="AH25" s="41">
         <v>1600000</v>
       </c>
+      <c r="AJ25" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK25" s="38">
+        <v>1424000</v>
+      </c>
     </row>
-    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>30</v>
       </c>
@@ -7185,18 +7302,27 @@
         <f t="array" aca="1" ref="AE26" ca="1">IFERROR([2]!CalculateINPC(AD26,[1]DT_BASE!$C$3,-1)*AC26,0)</f>
         <v>0</v>
       </c>
-      <c r="AF26" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AG26" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="AH26" s="50"/>
-      <c r="AI26">
+      <c r="AF26" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG26" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH26" s="33"/>
+      <c r="AI26" s="38">
         <v>900000</v>
       </c>
+      <c r="AJ26" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK26" s="38">
+        <v>617000</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>155</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7293,20 +7419,29 @@
         <f t="array" aca="1" ref="AE27" ca="1">IFERROR([2]!CalculateINPC(AD27,[1]DT_BASE!$C$3,-1)*AC27,0)</f>
         <v>0</v>
       </c>
-      <c r="AF27" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="AG27" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH27" s="49">
+      <c r="AF27" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG27" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH27" s="32">
         <v>12000000</v>
       </c>
-      <c r="AI27">
+      <c r="AI27" s="38">
         <v>8000000</v>
       </c>
+      <c r="AJ27" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK27" s="38">
+        <v>9520000</v>
+      </c>
+      <c r="AL27" s="44" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
         <v>30</v>
       </c>
@@ -7403,17 +7538,20 @@
         <f t="array" aca="1" ref="AE28" ca="1">IFERROR([2]!CalculateINPC(AD28,[1]DT_BASE!$C$3,-1)*AC28,0)</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG28" s="46" t="s">
+      <c r="AF28" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG28" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH28" s="46" t="s">
-        <v>144</v>
+      <c r="AH28" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM28" s="45">
+        <v>46138</v>
       </c>
     </row>
-    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>30</v>
       </c>
@@ -7508,15 +7646,18 @@
         <f t="array" aca="1" ref="AE29" ca="1">IFERROR([2]!CalculateINPC(AD29,[1]DT_BASE!$C$3,-1)*AC29,0)</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG29" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="AH29" s="46"/>
+      <c r="AF29" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG29" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH29" s="30"/>
+      <c r="AM29" s="45">
+        <v>46107</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>30</v>
       </c>
@@ -7611,17 +7752,20 @@
         <f t="array" aca="1" ref="AE30" ca="1">IFERROR([2]!CalculateINPC(AD30,[1]DT_BASE!$C$3,-1)*AC30,0)</f>
         <v>0</v>
       </c>
-      <c r="AF30" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG30" s="46" t="s">
+      <c r="AF30" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG30" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH30" s="46" t="s">
-        <v>144</v>
+      <c r="AH30" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM30" s="47" t="s">
+        <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>30</v>
       </c>
@@ -7716,15 +7860,21 @@
         <f t="array" aca="1" ref="AE31" ca="1">IFERROR([2]!CalculateINPC(AD31,[1]DT_BASE!$C$3,-1)*AC31,0)/2750000</f>
         <v>0</v>
       </c>
-      <c r="AF31" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG31" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH31" s="46"/>
+      <c r="AF31" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG31" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="38">
+        <v>350000</v>
+      </c>
+      <c r="AM31" s="47" t="s">
+        <v>160</v>
+      </c>
     </row>
-    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
         <v>30</v>
       </c>
@@ -7821,20 +7971,23 @@
         <f t="array" aca="1" ref="AE32" ca="1">IFERROR([2]!CalculateINPC(AD32,[1]DT_BASE!$C$3,-1)*AC32,0)</f>
         <v>0</v>
       </c>
-      <c r="AF32" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG32" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH32" s="47">
+      <c r="AF32" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG32" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH32" s="41">
         <v>1980000</v>
       </c>
-      <c r="AI32">
+      <c r="AI32" s="38">
         <v>1500000</v>
       </c>
+      <c r="AM32" s="47" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="33" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>30</v>
       </c>
@@ -7931,17 +8084,23 @@
         <f t="array" aca="1" ref="AE33" ca="1">IFERROR([2]!CalculateINPC(AD33,[1]DT_BASE!$C$3,-1)*AC33,0)</f>
         <v>0</v>
       </c>
-      <c r="AF33" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG33" s="46" t="s">
+      <c r="AF33" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG33" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH33" s="46" t="s">
-        <v>144</v>
+      <c r="AH33" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AJ33" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK33" s="38">
+        <v>130000</v>
       </c>
     </row>
-    <row r="34" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
         <v>30</v>
       </c>
@@ -8040,17 +8199,20 @@
         <f t="array" aca="1" ref="AE34" ca="1">IFERROR([2]!CalculateINPC(AD34,[1]DT_BASE!$C$3,-1)*AC34,0)</f>
         <v>0</v>
       </c>
-      <c r="AF34" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG34" s="46" t="s">
+      <c r="AF34" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG34" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH34" s="46" t="s">
-        <v>144</v>
+      <c r="AH34" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM34" s="47" t="s">
+        <v>162</v>
       </c>
     </row>
-    <row r="35" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>30</v>
       </c>
@@ -8145,17 +8307,20 @@
         <f t="array" aca="1" ref="AE35" ca="1">IFERROR([2]!CalculateINPC(AD35,[1]DT_BASE!$C$3,-1)*AC35,0)</f>
         <v>0</v>
       </c>
-      <c r="AF35" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG35" s="46" t="s">
+      <c r="AF35" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG35" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH35" s="46" t="s">
-        <v>144</v>
+      <c r="AH35" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM35" s="47" t="s">
+        <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>30</v>
       </c>
@@ -8250,17 +8415,20 @@
         <f t="array" aca="1" ref="AE36" ca="1">IFERROR([2]!CalculateINPC(AD36,[1]DT_BASE!$C$3,-1)*AC36,0)</f>
         <v>0</v>
       </c>
-      <c r="AF36" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG36" s="46" t="s">
+      <c r="AF36" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG36" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH36" s="46" t="s">
-        <v>144</v>
+      <c r="AH36" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="AM36" s="47" t="s">
+        <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>30</v>
       </c>
@@ -8359,17 +8527,20 @@
         <f t="array" aca="1" ref="AE37" ca="1">IFERROR([2]!CalculateINPC(AD37,[1]DT_BASE!$C$3,-1)*AC37,0)</f>
         <v>0</v>
       </c>
-      <c r="AF37" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG37" s="46" t="s">
+      <c r="AF37" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG37" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH37" s="46" t="s">
+      <c r="AH37" s="30" t="s">
         <v>37</v>
       </c>
+      <c r="AM37" s="47" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="38" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>30</v>
       </c>
@@ -8418,8 +8589,8 @@
       <c r="P38" s="25" t="e">
         <v>#N/A</v>
       </c>
-      <c r="Q38" s="25" t="e">
-        <v>#N/A</v>
+      <c r="Q38" s="25">
+        <v>0</v>
       </c>
       <c r="R38" s="25" t="e">
         <v>#N/A</v>
@@ -8463,17 +8634,17 @@
       <c r="AE38" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="AF38" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG38" s="46" t="s">
+      <c r="AF38" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG38" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH38" s="46" t="s">
+      <c r="AH38" s="30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:34" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>30</v>
       </c>
@@ -8568,640 +8739,27 @@
         <f t="array" aca="1" ref="AE39" ca="1">IFERROR([2]!CalculateINPC(AD39,[1]DT_BASE!$C$3,-1)*AC39,0)</f>
         <v>0</v>
       </c>
-      <c r="AF39" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="AG39" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH39" s="46"/>
+      <c r="AF39" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AG39" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="AH39" s="41">
+        <v>2500000</v>
+      </c>
+      <c r="AI39" s="38">
+        <v>2200000</v>
+      </c>
+      <c r="AL39" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM39" s="47" t="s">
+        <v>164</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE39" xr:uid="{82245A8F-1FD0-452B-9FFD-060B40FA72CD}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="25510"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A826AB59-3EB8-4F7C-AA66-A343392DE3EB}">
-  <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
-        <v>6896</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>130</v>
-      </c>
-      <c r="D1" s="41">
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="31">
-        <v>8112</v>
-      </c>
-      <c r="B2" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="42">
-        <v>25000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="43">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="44">
-        <v>22500000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="31">
-        <v>26999</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="44">
-        <v>13000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="31">
-        <v>35948</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="44">
-        <v>5200000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="31">
-        <v>20496</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="44">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="44">
-        <v>10500000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
-        <v>11142</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="31">
-        <v>4379</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="42">
-        <v>1600000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="31">
-        <v>1453</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="44">
-        <v>12000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="31">
-        <v>2629</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="31">
-        <v>7632</v>
-      </c>
-      <c r="B14" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="31">
-        <v>3222</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="44">
-        <v>1980000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="31">
-        <v>7047</v>
-      </c>
-      <c r="B16" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="31">
-        <v>51</v>
-      </c>
-      <c r="B17" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="31">
-        <v>147628</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="31">
-        <v>11444</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="31">
-        <v>15927</v>
-      </c>
-      <c r="B25" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="33">
-        <v>23697</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="33">
-        <v>9846</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="41" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="33">
-        <v>5377</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="33">
-        <v>4479</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="33">
-        <v>6193</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="33">
-        <v>579</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="33" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="34">
-        <v>1615</v>
-      </c>
-      <c r="B33" s="38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="34">
-        <v>25510</v>
-      </c>
-      <c r="B34" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="34">
-        <v>8701</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="31">
-        <v>145993</v>
-      </c>
-      <c r="B37" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="31">
-        <v>146005</v>
-      </c>
-      <c r="B38" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="B39" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="31">
-        <v>2164</v>
-      </c>
-      <c r="B41" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="31">
-        <v>10565</v>
-      </c>
-      <c r="B42" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="32">
-        <v>3495</v>
-      </c>
-      <c r="B43" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C43" s="31" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C44" s="31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C45" s="31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C46" s="31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:AJ39" xr:uid="{82245A8F-1FD0-452B-9FFD-060B40FA72CD}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
